--- a/libertadores/datasets_liberta/perdedores_fase_4.xlsx
+++ b/libertadores/datasets_liberta/perdedores_fase_4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>jogo</t>
   </si>
@@ -31,7 +31,10 @@
     <t>Jogo 2 (JG2)</t>
   </si>
   <si>
-    <t>EMPATE</t>
+    <t>Fedato Futebol Clube</t>
+  </si>
+  <si>
+    <t>TEAM LOPES 99</t>
   </si>
 </sst>
 </file>
@@ -410,13 +413,19 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2">
+        <v>18642587</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>479510</v>
       </c>
     </row>
   </sheetData>
